--- a/examples/HFP_joe.xlsx
+++ b/examples/HFP_joe.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,35 +448,40 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>net inv</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -490,15 +495,18 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
         <v>7000</v>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -508,15 +516,18 @@
       <c r="C3" t="n">
         <v>0</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
         <v>7000</v>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -526,15 +537,18 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>7500</v>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -544,15 +558,18 @@
       <c r="C5" t="n">
         <v>0</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="n">
         <v>7500</v>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -562,15 +579,18 @@
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,15 +602,18 @@
       <c r="C7" t="n">
         <v>0</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="n">
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
         <v>15000</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="n">
         <v>-40000</v>
       </c>
     </row>
@@ -604,15 +627,18 @@
       <c r="C8" t="n">
         <v>0</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="n">
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
         <v>15000</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -624,13 +650,16 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -640,13 +669,16 @@
       <c r="C10" t="n">
         <v>0</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -656,13 +688,16 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -672,13 +707,16 @@
       <c r="C12" t="n">
         <v>0</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -688,13 +726,16 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -704,13 +745,16 @@
       <c r="C14" t="n">
         <v>0</v>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -720,13 +764,16 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -736,13 +783,16 @@
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -752,13 +802,16 @@
       <c r="C17" t="n">
         <v>0</v>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -768,13 +821,16 @@
       <c r="C18" t="n">
         <v>0</v>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -784,13 +840,16 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -800,13 +859,16 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -816,13 +878,16 @@
       <c r="C21" t="n">
         <v>0</v>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -832,13 +897,16 @@
       <c r="C22" t="n">
         <v>0</v>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -848,13 +916,16 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -864,13 +935,16 @@
       <c r="C24" t="n">
         <v>0</v>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -880,13 +954,16 @@
       <c r="C25" t="n">
         <v>0</v>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -896,13 +973,16 @@
       <c r="C26" t="n">
         <v>0</v>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -912,13 +992,16 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -928,13 +1011,16 @@
       <c r="C28" t="n">
         <v>0</v>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -944,13 +1030,16 @@
       <c r="C29" t="n">
         <v>0</v>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -960,13 +1049,16 @@
       <c r="C30" t="n">
         <v>0</v>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -976,13 +1068,16 @@
       <c r="C31" t="n">
         <v>0</v>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -992,13 +1087,16 @@
       <c r="C32" t="n">
         <v>0</v>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1008,13 +1106,16 @@
       <c r="C33" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1024,13 +1125,16 @@
       <c r="C34" t="n">
         <v>0</v>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1040,13 +1144,16 @@
       <c r="C35" t="n">
         <v>0</v>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1056,13 +1163,16 @@
       <c r="C36" t="n">
         <v>0</v>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/HFP_joe.xlsx
+++ b/examples/HFP_joe.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,111 +486,96 @@
           <t>big-ticket items</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>HSA ctrb</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>7000</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>7000</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>7500</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>7500</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -605,16 +590,14 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>15000</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
         <v>-40000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4500</v>
       </c>
     </row>
     <row r="8">
@@ -630,15 +613,12 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>15000</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>4500</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -653,526 +633,387 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1236,7 +1077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1286,6 +1127,39 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Rental property</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>real estate</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E2" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>280000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/HFP_joe.xlsx
+++ b/examples/HFP_joe.xlsx
@@ -1151,7 +1151,7 @@
         <v>280000</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>2032</v>

--- a/examples/HFP_joe.xlsx
+++ b/examples/HFP_joe.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Joe" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Joe" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Debts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fixed Assets" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,16 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -47,21 +44,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,66 +415,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>anticipated wages</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>other inc</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>net inv</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>taxable ctrb</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>401k ctrb</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Roth 401k ctrb</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IRA ctrb</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Roth IRA ctrb</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Roth conv</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -496,16 +489,26 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>7000</v>
       </c>
-      <c r="L2" t="n">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -513,16 +516,26 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>7000</v>
       </c>
-      <c r="L3" t="n">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -530,16 +543,26 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>7500</v>
       </c>
-      <c r="L4" t="n">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -547,16 +570,26 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>7500</v>
       </c>
-      <c r="L5" t="n">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -564,16 +597,26 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="L6" t="n">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -590,13 +633,21 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>15000</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>-40000</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -613,10 +664,19 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>15000</v>
       </c>
-      <c r="L8" t="n">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -633,7 +693,17 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -641,13 +711,24 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -655,13 +736,24 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -669,13 +761,24 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,13 +786,24 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -697,13 +811,24 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -711,13 +836,24 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -725,13 +861,24 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -739,13 +886,24 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -753,13 +911,24 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -767,13 +936,24 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -781,13 +961,24 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
+      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -795,13 +986,24 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -809,13 +1011,24 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -823,13 +1036,24 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -837,13 +1061,24 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -851,13 +1086,24 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -865,13 +1111,24 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -879,13 +1136,24 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -893,13 +1161,24 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -907,13 +1186,24 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -921,13 +1211,24 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -935,13 +1236,24 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -949,13 +1261,24 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -963,13 +1286,24 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -977,13 +1311,24 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -991,13 +1336,24 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1005,13 +1361,24 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1030,37 +1397,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>term</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
@@ -1081,47 +1448,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>rate</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>yod</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>commission</t>
         </is>

--- a/examples/HFP_joe.xlsx
+++ b/examples/HFP_joe.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,15 +471,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HSA ctrb</t>
         </is>
@@ -489,26 +494,19 @@
       <c r="A2" t="n">
         <v>2021</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
         <v>7000</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -516,26 +514,19 @@
       <c r="A3" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
         <v>7000</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -543,26 +534,19 @@
       <c r="A4" t="n">
         <v>2023</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
         <v>7500</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -570,26 +554,19 @@
       <c r="A5" t="n">
         <v>2024</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
         <v>7500</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -597,26 +574,19 @@
       <c r="A6" t="n">
         <v>2025</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
         <v>7500</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -633,21 +603,16 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>15000</v>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>-40000</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -664,19 +629,13 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>15000</v>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>4500</v>
       </c>
     </row>
@@ -693,17 +652,10 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -711,24 +663,16 @@
       <c r="A10" t="n">
         <v>2029</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -736,24 +680,16 @@
       <c r="A11" t="n">
         <v>2030</v>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -761,24 +697,16 @@
       <c r="A12" t="n">
         <v>2031</v>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -786,24 +714,16 @@
       <c r="A13" t="n">
         <v>2032</v>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -811,24 +731,16 @@
       <c r="A14" t="n">
         <v>2033</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -836,24 +748,16 @@
       <c r="A15" t="n">
         <v>2034</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -861,24 +765,16 @@
       <c r="A16" t="n">
         <v>2035</v>
       </c>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -886,24 +782,16 @@
       <c r="A17" t="n">
         <v>2036</v>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -911,24 +799,16 @@
       <c r="A18" t="n">
         <v>2037</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -936,24 +816,16 @@
       <c r="A19" t="n">
         <v>2038</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -961,24 +833,16 @@
       <c r="A20" t="n">
         <v>2039</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -986,24 +850,16 @@
       <c r="A21" t="n">
         <v>2040</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1011,24 +867,16 @@
       <c r="A22" t="n">
         <v>2041</v>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1036,24 +884,16 @@
       <c r="A23" t="n">
         <v>2042</v>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1061,24 +901,16 @@
       <c r="A24" t="n">
         <v>2043</v>
       </c>
-      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1086,24 +918,16 @@
       <c r="A25" t="n">
         <v>2044</v>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1111,24 +935,16 @@
       <c r="A26" t="n">
         <v>2045</v>
       </c>
-      <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1136,24 +952,16 @@
       <c r="A27" t="n">
         <v>2046</v>
       </c>
-      <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1161,24 +969,16 @@
       <c r="A28" t="n">
         <v>2047</v>
       </c>
-      <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1186,24 +986,16 @@
       <c r="A29" t="n">
         <v>2048</v>
       </c>
-      <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1211,24 +1003,16 @@
       <c r="A30" t="n">
         <v>2049</v>
       </c>
-      <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1236,24 +1020,16 @@
       <c r="A31" t="n">
         <v>2050</v>
       </c>
-      <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1261,24 +1037,16 @@
       <c r="A32" t="n">
         <v>2051</v>
       </c>
-      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1286,24 +1054,16 @@
       <c r="A33" t="n">
         <v>2052</v>
       </c>
-      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1311,24 +1071,16 @@
       <c r="A34" t="n">
         <v>2053</v>
       </c>
-      <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1336,24 +1088,16 @@
       <c r="A35" t="n">
         <v>2054</v>
       </c>
-      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1361,24 +1105,16 @@
       <c r="A36" t="n">
         <v>2055</v>
       </c>
-      <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
